--- a/Donnees/Statistiques Démographiques et sociales/Santé/Tableaux Santé de la mère et de l'enfant_Portail (1).xlsx
+++ b/Donnees/Statistiques Démographiques et sociales/Santé/Tableaux Santé de la mère et de l'enfant_Portail (1).xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9780E579-8827-4287-9D61-BC82D721EA93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A403AA83-1310-4E8A-A442-614AE9BD05DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TS1" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="68">
   <si>
     <t>Wilaya</t>
   </si>
@@ -98,9 +98,6 @@
   </si>
   <si>
     <t xml:space="preserve">Hodh Chargui </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source : ANSADE, EDSM 2019-2021 </t>
   </si>
   <si>
     <t>Tableau : Pourcentage de femmes de 15-49 ans qui ont effectué au moins 4 visites prénatales dont au moins une avec un prestataire de santé qualifié; par wilaya selon la qualité des soins prénatals effectué.</t>
@@ -948,7 +945,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B1" s="40"/>
       <c r="C1" s="40"/>
@@ -962,33 +959,33 @@
     <row r="2" spans="1:9" ht="79.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
       <c r="B2" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>32</v>
-      </c>
       <c r="I2" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B3" s="4">
         <v>24.4</v>
@@ -1465,7 +1462,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="46" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="B20" s="47"/>
       <c r="C20" s="47"/>
@@ -1499,7 +1496,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -1508,18 +1505,18 @@
     <row r="2" spans="1:4" ht="106.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="41"/>
       <c r="B2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B3" s="10">
         <v>37.6</v>
@@ -1776,7 +1773,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="45" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B1" s="45"/>
       <c r="C1" s="45"/>
@@ -1788,27 +1785,27 @@
     <row r="2" spans="1:7" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="45"/>
       <c r="B2" s="45" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="D2" s="45" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="45" t="s">
+      <c r="E2" s="45" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="E2" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="F2" s="45" t="s">
-        <v>64</v>
-      </c>
       <c r="G2" s="45" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="45" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B3" s="45">
         <v>67.7</v>
@@ -2249,36 +2246,36 @@
     <row r="2" spans="1:10" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
       <c r="B2" s="39" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C2" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="39" t="s">
+      <c r="E2" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="39" t="s">
+      <c r="F2" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="39" t="s">
+      <c r="G2" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="G2" s="39" t="s">
+      <c r="H2" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="H2" s="39" t="s">
+      <c r="I2" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="I2" s="39" t="s">
-        <v>42</v>
-      </c>
       <c r="J2" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B3" s="4">
         <v>11.1</v>
@@ -2826,7 +2823,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" s="39"/>
       <c r="C1" s="39"/>
@@ -2835,10 +2832,10 @@
     <row r="2" spans="1:4" ht="79.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
       <c r="B2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>8</v>
@@ -2846,7 +2843,7 @@
     </row>
     <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B3" s="4">
         <v>3.2</v>
@@ -3113,7 +3110,7 @@
     </row>
     <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B3" s="25">
         <v>37.9</v>
@@ -3346,42 +3343,42 @@
     <row r="3" spans="1:12" ht="68.400000000000006" x14ac:dyDescent="0.3">
       <c r="A3" s="8"/>
       <c r="B3" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="44" t="s">
+      <c r="D3" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="D3" s="44" t="s">
+      <c r="E3" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="E3" s="44" t="s">
+      <c r="F3" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="44" t="s">
+      <c r="G3" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="G3" s="44" t="s">
+      <c r="H3" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="H3" s="44" t="s">
+      <c r="I3" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="I3" s="44" t="s">
+      <c r="J3" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="J3" s="44" t="s">
+      <c r="K3" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="K3" s="44" t="s">
+      <c r="L3" s="44" t="s">
         <v>54</v>
-      </c>
-      <c r="L3" s="44" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="37" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B4" s="10">
         <v>8.6</v>

--- a/Donnees/Statistiques Démographiques et sociales/Santé/Tableaux Santé de la mère et de l'enfant_Portail (1).xlsx
+++ b/Donnees/Statistiques Démographiques et sociales/Santé/Tableaux Santé de la mère et de l'enfant_Portail (1).xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A403AA83-1310-4E8A-A442-614AE9BD05DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72E9763C-1A8F-4EC7-9E8E-301F8AC116AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TS1" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="69">
   <si>
     <t>Wilaya</t>
   </si>
@@ -55,9 +55,6 @@
     <t>Pourcentage accouché par césarienne</t>
   </si>
   <si>
-    <t xml:space="preserve">Source:  ANSADE,  EDSM 2019-2021 </t>
-  </si>
-  <si>
     <t xml:space="preserve">Hodh  Chargui </t>
   </si>
   <si>
@@ -91,22 +88,10 @@
     <t>Aucun vaccin</t>
   </si>
   <si>
-    <t>Tableau : Pourcentage d'enfants de 12-23 mois par wilya selon le statut de vaccination</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tableau: Pourcentage d’enfants de moins de 5 ans par Wilaya selon les trois indices anthropométriques de mesure de l’état nutritionnel : la taille-pour-âge, le poids-pour-taille et le poids-pour-âge,  </t>
-  </si>
-  <si>
     <t xml:space="preserve">Hodh Chargui </t>
   </si>
   <si>
-    <t>Tableau : Pourcentage de femmes de 15-49 ans qui ont effectué au moins 4 visites prénatales dont au moins une avec un prestataire de santé qualifié; par wilaya selon la qualité des soins prénatals effectué.</t>
-  </si>
-  <si>
     <t>Mauritanie</t>
-  </si>
-  <si>
-    <t>Tableau: Pourcentage de naissances vivantes ayant eu lieu au cours des 5 dernières années ayant précédé l'enquête (EDSM) accouchées par césarienne par Wilaya selon le moment de la prise de décision</t>
   </si>
   <si>
     <t>Prestataire de soins prénatals~Infirmière-sage-femme</t>
@@ -238,9 +223,6 @@
     <t>Prestataire de soins prénatals~Agent de santé communautaire-village</t>
   </si>
   <si>
-    <t>Tableau: Répartition (en %) des naissances vivantes ayant eu lieu au cours des 5 années ayant précédé l'enquête(EDSM) par Wilaya selon le lieu de l'accouchement</t>
-  </si>
-  <si>
     <t>Pourcentage dont l'accouchement a été assisté par un prestataire qualifié</t>
   </si>
   <si>
@@ -265,7 +247,28 @@
     <t>Etablissement de santé~Autre</t>
   </si>
   <si>
-    <t xml:space="preserve">Tableau: Pourcentage de femmes de 15-49 ans qui ont reçu des soins prénatals par wilaya selon par type de prestataire de santé vu durant la grossesse  </t>
+    <t>Source : EDSM/2019</t>
+  </si>
+  <si>
+    <t>Tableau 1.3.3: Pourcentage de femmes de 15-49 ans qui ont reçu des soins prénatals durant la grossesse par wilaya selon le type du personnel de santé consulté</t>
+  </si>
+  <si>
+    <t>Tableau 1.3.4: Pourcentage de femmes 15-49 ans qui ont effectué au moins 4 visites prénatales dont au moins une avec un prestataire de santé qualifié par wilaya selon la qualité des soins prénatals effectué.</t>
+  </si>
+  <si>
+    <t>Tableau 1.3.5: Répartition (en %) des naissances vivantes ayant eu lieu au cours des 5 années ayant précédé l'enquête (EDSM) par Wilaya selon le lieu de l'accouchement</t>
+  </si>
+  <si>
+    <t>Tableau 1.3.6: Répartition (en %) des naissances vivantes ayant eu lieu au cours des 5 années ayant précédé l'enquête (EDSM) par Wilaya selon le type de personnel ayant assisté l'accouchement,</t>
+  </si>
+  <si>
+    <t>Tableau 1.3.7: Pourcentage de naissances vivantes ayant eu lieu au cours des 5 dernières années ayant précédé l'enquête (EDSM) accouchées par césarienne par Wilaya selon le moment de la prise de décision</t>
+  </si>
+  <si>
+    <t>Tableau 1.3.8: Pourcentage d'enfants de 12-23 mois par wilaya selon le statut de vaccination</t>
+  </si>
+  <si>
+    <t>Tableau 1.3.9: Pourcentage d’enfants de moins de 5 ans par Wilaya selon les trois indices anthropométriques de mesure de l’état nutritionnel : la taille-pour-âge, le poids-pour-taille et le poids-pour-âge,</t>
   </si>
 </sst>
 </file>
@@ -275,7 +278,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -331,6 +334,12 @@
     </font>
     <font>
       <sz val="4"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -516,7 +525,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -613,9 +622,6 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -648,6 +654,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -944,48 +956,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="40" t="s">
-        <v>67</v>
-      </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
+      <c r="A1" s="39" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
     </row>
     <row r="2" spans="1:9" ht="79.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
       <c r="B2" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="19" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B3" s="4">
         <v>24.4</v>
@@ -1027,7 +1039,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="20" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B5" s="2">
         <v>22.8</v>
@@ -1056,7 +1068,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" s="8">
         <v>21.2</v>
@@ -1288,7 +1300,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" s="8">
         <v>7.2</v>
@@ -1317,7 +1329,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15" s="8">
         <v>34.5</v>
@@ -1346,7 +1358,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B16" s="8">
         <v>35</v>
@@ -1375,7 +1387,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" s="8">
         <v>26</v>
@@ -1404,7 +1416,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B18" s="8">
         <v>43.2</v>
@@ -1433,7 +1445,7 @@
     </row>
     <row r="19" spans="1:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B19" s="10">
         <v>35.799999999999997</v>
@@ -1461,17 +1473,17 @@
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="47"/>
-      <c r="C20" s="47"/>
-      <c r="D20" s="47"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="47"/>
-      <c r="H20" s="47"/>
-      <c r="I20" s="47"/>
+      <c r="A20" s="45" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="46"/>
+      <c r="C20" s="46"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="46"/>
+      <c r="G20" s="46"/>
+      <c r="H20" s="46"/>
+      <c r="I20" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1496,27 +1508,27 @@
   <sheetData>
     <row r="1" spans="1:4" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
     </row>
     <row r="2" spans="1:4" ht="106.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="41"/>
+      <c r="A2" s="40"/>
       <c r="B2" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="19" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B3" s="10">
         <v>37.6</v>
@@ -1538,7 +1550,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="20" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B5" s="8">
         <v>14.9</v>
@@ -1552,7 +1564,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" s="8">
         <v>28.8</v>
@@ -1664,7 +1676,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" s="8">
         <v>38.299999999999997</v>
@@ -1678,7 +1690,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15" s="8">
         <v>25.1</v>
@@ -1692,7 +1704,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B16" s="17">
         <v>44.833333333333336</v>
@@ -1706,7 +1718,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" s="8">
         <v>50.8</v>
@@ -1720,7 +1732,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B18" s="8">
         <v>42.9</v>
@@ -1734,7 +1746,7 @@
     </row>
     <row r="19" spans="1:4" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B19" s="10">
         <v>40.799999999999997</v>
@@ -1748,7 +1760,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1772,426 +1784,426 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="45" t="s">
-        <v>58</v>
-      </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
+      <c r="A1" s="44" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
     </row>
     <row r="2" spans="1:7" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45" t="s">
+      <c r="A2" s="44"/>
+      <c r="B2" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="44" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="F2" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="G2" s="44" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="44">
+        <v>67.7</v>
+      </c>
+      <c r="C3" s="44">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="D3" s="44">
+        <v>29.8</v>
+      </c>
+      <c r="E3" s="44">
+        <v>0.2</v>
+      </c>
+      <c r="F3" s="44">
+        <v>100</v>
+      </c>
+      <c r="G3" s="44">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+    </row>
+    <row r="5" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="44">
+        <v>44.5</v>
+      </c>
+      <c r="C5" s="44">
+        <v>0.7</v>
+      </c>
+      <c r="D5" s="44">
+        <v>54.7</v>
+      </c>
+      <c r="E5" s="44">
+        <v>0.1</v>
+      </c>
+      <c r="F5" s="44">
+        <v>100</v>
+      </c>
+      <c r="G5" s="44">
+        <v>45.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="44">
+        <v>50.7</v>
+      </c>
+      <c r="C6" s="44">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D6" s="44">
+        <v>48.2</v>
+      </c>
+      <c r="E6" s="44">
+        <v>0</v>
+      </c>
+      <c r="F6" s="44">
+        <v>100</v>
+      </c>
+      <c r="G6" s="44">
+        <v>51.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="44">
+        <v>59.2</v>
+      </c>
+      <c r="C7" s="44">
+        <v>1.7</v>
+      </c>
+      <c r="D7" s="44">
+        <v>39</v>
+      </c>
+      <c r="E7" s="44">
+        <v>0.1</v>
+      </c>
+      <c r="F7" s="44">
+        <v>100</v>
+      </c>
+      <c r="G7" s="44">
+        <v>60.9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="44" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="44">
+        <v>64.599999999999994</v>
+      </c>
+      <c r="C8" s="44">
+        <v>0.6</v>
+      </c>
+      <c r="D8" s="44">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="E8" s="44">
+        <v>1</v>
+      </c>
+      <c r="F8" s="44">
+        <v>100</v>
+      </c>
+      <c r="G8" s="44">
+        <v>65.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="44">
+        <v>77.7</v>
+      </c>
+      <c r="C9" s="44">
+        <v>1.3</v>
+      </c>
+      <c r="D9" s="44">
+        <v>20.7</v>
+      </c>
+      <c r="E9" s="44">
+        <v>0.2</v>
+      </c>
+      <c r="F9" s="44">
+        <v>100</v>
+      </c>
+      <c r="G9" s="44">
+        <v>79.099999999999994</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="44">
+        <v>87.6</v>
+      </c>
+      <c r="C10" s="44">
+        <v>2.4</v>
+      </c>
+      <c r="D10" s="44">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="E10" s="44">
+        <v>0.2</v>
+      </c>
+      <c r="F10" s="44">
+        <v>100</v>
+      </c>
+      <c r="G10" s="44">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="44">
+        <v>73.2</v>
+      </c>
+      <c r="C11" s="44">
+        <v>1.2</v>
+      </c>
+      <c r="D11" s="44">
+        <v>25.6</v>
+      </c>
+      <c r="E11" s="44">
+        <v>0</v>
+      </c>
+      <c r="F11" s="44">
+        <v>100</v>
+      </c>
+      <c r="G11" s="44">
+        <v>74.400000000000006</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="44" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="44">
+        <v>92.2</v>
+      </c>
+      <c r="C12" s="44">
+        <v>5.9</v>
+      </c>
+      <c r="D12" s="44">
+        <v>1.9</v>
+      </c>
+      <c r="E12" s="44">
+        <v>0</v>
+      </c>
+      <c r="F12" s="44">
+        <v>100</v>
+      </c>
+      <c r="G12" s="44">
+        <v>98.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="44" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="44">
+        <v>62.4</v>
+      </c>
+      <c r="C13" s="44">
+        <v>0.2</v>
+      </c>
+      <c r="D13" s="44">
+        <v>37.1</v>
+      </c>
+      <c r="E13" s="44">
+        <v>0.3</v>
+      </c>
+      <c r="F13" s="44">
+        <v>100</v>
+      </c>
+      <c r="G13" s="44">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="44">
+        <v>49.4</v>
+      </c>
+      <c r="C14" s="44">
+        <v>0.1</v>
+      </c>
+      <c r="D14" s="44">
+        <v>50.2</v>
+      </c>
+      <c r="E14" s="44">
+        <v>0.3</v>
+      </c>
+      <c r="F14" s="44">
+        <v>100</v>
+      </c>
+      <c r="G14" s="44">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="44" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="44">
+        <v>90.8</v>
+      </c>
+      <c r="C15" s="44">
+        <v>6.5</v>
+      </c>
+      <c r="D15" s="44">
+        <v>2.7</v>
+      </c>
+      <c r="E15" s="44">
+        <v>0</v>
+      </c>
+      <c r="F15" s="44">
+        <v>100</v>
+      </c>
+      <c r="G15" s="44">
+        <v>97.3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="44">
+        <v>91.6</v>
+      </c>
+      <c r="C16" s="44">
+        <v>6.3999999999999995</v>
+      </c>
+      <c r="D16" s="44">
+        <v>1.9</v>
+      </c>
+      <c r="E16" s="44">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="F16" s="44">
+        <v>100</v>
+      </c>
+      <c r="G16" s="44">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A17" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="44">
+        <v>89.3</v>
+      </c>
+      <c r="C17" s="44">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="D17" s="44">
+        <v>1.9</v>
+      </c>
+      <c r="E17" s="44">
+        <v>0</v>
+      </c>
+      <c r="F17" s="44">
+        <v>100</v>
+      </c>
+      <c r="G17" s="44">
+        <v>98.1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="44">
+        <v>91.5</v>
+      </c>
+      <c r="C18" s="44">
+        <v>7.1</v>
+      </c>
+      <c r="D18" s="44">
+        <v>1.3</v>
+      </c>
+      <c r="E18" s="44">
+        <v>0.1</v>
+      </c>
+      <c r="F18" s="44">
+        <v>100</v>
+      </c>
+      <c r="G18" s="44">
+        <v>98.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="44">
+        <v>94.1</v>
+      </c>
+      <c r="C19" s="44">
+        <v>3.3</v>
+      </c>
+      <c r="D19" s="44">
+        <v>2.6</v>
+      </c>
+      <c r="E19" s="44">
+        <v>0.1</v>
+      </c>
+      <c r="F19" s="44">
+        <v>100</v>
+      </c>
+      <c r="G19" s="44">
+        <v>97.4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A20" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="D2" s="45" t="s">
-        <v>62</v>
-      </c>
-      <c r="E2" s="45" t="s">
-        <v>66</v>
-      </c>
-      <c r="F2" s="45" t="s">
-        <v>63</v>
-      </c>
-      <c r="G2" s="45" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="45" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="45">
-        <v>67.7</v>
-      </c>
-      <c r="C3" s="45">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="D3" s="45">
-        <v>29.8</v>
-      </c>
-      <c r="E3" s="45">
-        <v>0.2</v>
-      </c>
-      <c r="F3" s="45">
-        <v>100</v>
-      </c>
-      <c r="G3" s="45">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="45" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-    </row>
-    <row r="5" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="45" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="45">
-        <v>44.5</v>
-      </c>
-      <c r="C5" s="45">
-        <v>0.7</v>
-      </c>
-      <c r="D5" s="45">
-        <v>54.7</v>
-      </c>
-      <c r="E5" s="45">
-        <v>0.1</v>
-      </c>
-      <c r="F5" s="45">
-        <v>100</v>
-      </c>
-      <c r="G5" s="45">
-        <v>45.2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="45" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="45">
-        <v>50.7</v>
-      </c>
-      <c r="C6" s="45">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="D6" s="45">
-        <v>48.2</v>
-      </c>
-      <c r="E6" s="45">
-        <v>0</v>
-      </c>
-      <c r="F6" s="45">
-        <v>100</v>
-      </c>
-      <c r="G6" s="45">
-        <v>51.8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="45">
-        <v>59.2</v>
-      </c>
-      <c r="C7" s="45">
-        <v>1.7</v>
-      </c>
-      <c r="D7" s="45">
-        <v>39</v>
-      </c>
-      <c r="E7" s="45">
-        <v>0.1</v>
-      </c>
-      <c r="F7" s="45">
-        <v>100</v>
-      </c>
-      <c r="G7" s="45">
-        <v>60.9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8" s="45">
-        <v>64.599999999999994</v>
-      </c>
-      <c r="C8" s="45">
-        <v>0.6</v>
-      </c>
-      <c r="D8" s="45">
-        <v>33.799999999999997</v>
-      </c>
-      <c r="E8" s="45">
-        <v>1</v>
-      </c>
-      <c r="F8" s="45">
-        <v>100</v>
-      </c>
-      <c r="G8" s="45">
-        <v>65.2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="45" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="45">
-        <v>77.7</v>
-      </c>
-      <c r="C9" s="45">
-        <v>1.3</v>
-      </c>
-      <c r="D9" s="45">
-        <v>20.7</v>
-      </c>
-      <c r="E9" s="45">
-        <v>0.2</v>
-      </c>
-      <c r="F9" s="45">
-        <v>100</v>
-      </c>
-      <c r="G9" s="45">
-        <v>79.099999999999994</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="45" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="45">
-        <v>87.6</v>
-      </c>
-      <c r="C10" s="45">
-        <v>2.4</v>
-      </c>
-      <c r="D10" s="45">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="E10" s="45">
-        <v>0.2</v>
-      </c>
-      <c r="F10" s="45">
-        <v>100</v>
-      </c>
-      <c r="G10" s="45">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" s="45">
-        <v>73.2</v>
-      </c>
-      <c r="C11" s="45">
-        <v>1.2</v>
-      </c>
-      <c r="D11" s="45">
-        <v>25.6</v>
-      </c>
-      <c r="E11" s="45">
-        <v>0</v>
-      </c>
-      <c r="F11" s="45">
-        <v>100</v>
-      </c>
-      <c r="G11" s="45">
-        <v>74.400000000000006</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="45" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="45">
-        <v>92.2</v>
-      </c>
-      <c r="C12" s="45">
-        <v>5.9</v>
-      </c>
-      <c r="D12" s="45">
-        <v>1.9</v>
-      </c>
-      <c r="E12" s="45">
-        <v>0</v>
-      </c>
-      <c r="F12" s="45">
-        <v>100</v>
-      </c>
-      <c r="G12" s="45">
-        <v>98.1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" s="45">
-        <v>62.4</v>
-      </c>
-      <c r="C13" s="45">
-        <v>0.2</v>
-      </c>
-      <c r="D13" s="45">
-        <v>37.1</v>
-      </c>
-      <c r="E13" s="45">
-        <v>0.3</v>
-      </c>
-      <c r="F13" s="45">
-        <v>100</v>
-      </c>
-      <c r="G13" s="45">
-        <v>62.6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="45">
-        <v>49.4</v>
-      </c>
-      <c r="C14" s="45">
-        <v>0.1</v>
-      </c>
-      <c r="D14" s="45">
-        <v>50.2</v>
-      </c>
-      <c r="E14" s="45">
-        <v>0.3</v>
-      </c>
-      <c r="F14" s="45">
-        <v>100</v>
-      </c>
-      <c r="G14" s="45">
-        <v>49.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="45" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="45">
-        <v>90.8</v>
-      </c>
-      <c r="C15" s="45">
-        <v>6.5</v>
-      </c>
-      <c r="D15" s="45">
-        <v>2.7</v>
-      </c>
-      <c r="E15" s="45">
-        <v>0</v>
-      </c>
-      <c r="F15" s="45">
-        <v>100</v>
-      </c>
-      <c r="G15" s="45">
-        <v>97.3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="45">
-        <v>91.6</v>
-      </c>
-      <c r="C16" s="45">
-        <v>6.3999999999999995</v>
-      </c>
-      <c r="D16" s="45">
-        <v>1.9</v>
-      </c>
-      <c r="E16" s="45">
-        <v>6.7000000000000004E-2</v>
-      </c>
-      <c r="F16" s="45">
-        <v>100</v>
-      </c>
-      <c r="G16" s="45">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="45" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="45">
-        <v>89.3</v>
-      </c>
-      <c r="C17" s="45">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="D17" s="45">
-        <v>1.9</v>
-      </c>
-      <c r="E17" s="45">
-        <v>0</v>
-      </c>
-      <c r="F17" s="45">
-        <v>100</v>
-      </c>
-      <c r="G17" s="45">
-        <v>98.1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="45">
-        <v>91.5</v>
-      </c>
-      <c r="C18" s="45">
-        <v>7.1</v>
-      </c>
-      <c r="D18" s="45">
-        <v>1.3</v>
-      </c>
-      <c r="E18" s="45">
-        <v>0.1</v>
-      </c>
-      <c r="F18" s="45">
-        <v>100</v>
-      </c>
-      <c r="G18" s="45">
-        <v>98.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="45" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" s="45">
-        <v>94.1</v>
-      </c>
-      <c r="C19" s="45">
-        <v>3.3</v>
-      </c>
-      <c r="D19" s="45">
-        <v>2.6</v>
-      </c>
-      <c r="E19" s="45">
-        <v>0.1</v>
-      </c>
-      <c r="F19" s="45">
-        <v>100</v>
-      </c>
-      <c r="G19" s="45">
-        <v>97.4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="45"/>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="45"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
     </row>
     <row r="21" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21"/>
@@ -2230,52 +2242,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
+      <c r="A1" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
     </row>
     <row r="2" spans="1:10" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
-      <c r="B2" s="39" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" s="39" t="s">
+      <c r="B2" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="39" t="s">
+      <c r="I2" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="F2" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="G2" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="H2" s="39" t="s">
-        <v>40</v>
-      </c>
-      <c r="I2" s="39" t="s">
-        <v>41</v>
-      </c>
       <c r="J2" s="6" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B3" s="4">
         <v>11.1</v>
@@ -2301,7 +2313,7 @@
       <c r="I3" s="4">
         <v>100</v>
       </c>
-      <c r="J3" s="39">
+      <c r="J3" s="38">
         <v>70.400000000000006</v>
       </c>
     </row>
@@ -2321,7 +2333,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B5" s="8">
         <v>8.6</v>
@@ -2353,7 +2365,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" s="8">
         <v>5.4</v>
@@ -2609,7 +2621,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" s="8">
         <v>2.2000000000000002</v>
@@ -2641,7 +2653,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15" s="8">
         <v>23.3</v>
@@ -2673,7 +2685,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B16" s="17">
         <v>20.066666666666666</v>
@@ -2705,7 +2717,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" s="8">
         <v>16.600000000000001</v>
@@ -2737,7 +2749,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B18" s="8">
         <v>28.8</v>
@@ -2769,7 +2781,7 @@
     </row>
     <row r="19" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B19" s="10">
         <v>14.8</v>
@@ -2801,7 +2813,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -2823,19 +2835,19 @@
   <sheetData>
     <row r="1" spans="1:4" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
+        <v>66</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
     </row>
     <row r="2" spans="1:4" ht="79.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
       <c r="B2" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>8</v>
@@ -2843,7 +2855,7 @@
     </row>
     <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B3" s="4">
         <v>3.2</v>
@@ -2865,7 +2877,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" s="8">
         <v>0.4</v>
@@ -2879,7 +2891,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" s="17">
         <v>1</v>
@@ -2991,7 +3003,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" s="8">
         <v>0.6</v>
@@ -3005,7 +3017,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15" s="8">
         <v>7.8</v>
@@ -3019,7 +3031,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B16" s="17">
         <v>8.0666666666666682</v>
@@ -3033,7 +3045,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" s="8">
         <v>7.2</v>
@@ -3047,7 +3059,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B18" s="8">
         <v>11.4</v>
@@ -3061,7 +3073,7 @@
     </row>
     <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B19" s="10">
         <v>5.6</v>
@@ -3075,7 +3087,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -3085,7 +3097,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92EAACF3-04C7-4F6C-A1FD-4A63096D0148}">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.6640625" customWidth="1"/>
@@ -3093,24 +3105,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
+      <c r="A1" s="42" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
     </row>
     <row r="2" spans="1:3" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="22"/>
       <c r="B2" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="24" t="s">
         <v>19</v>
-      </c>
-      <c r="C2" s="24" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="22" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B3" s="25">
         <v>37.9</v>
@@ -3128,7 +3140,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" s="30">
         <v>23.1</v>
@@ -3139,7 +3151,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" s="32">
         <v>47.1</v>
@@ -3227,7 +3239,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" s="32">
         <v>49.1</v>
@@ -3238,7 +3250,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15" s="32">
         <v>42.4</v>
@@ -3249,18 +3261,18 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B16" s="34">
         <v>34.9</v>
       </c>
-      <c r="C16" s="38">
+      <c r="C16" s="37">
         <v>5.9669999999999996</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" s="32">
         <v>28.3</v>
@@ -3271,7 +3283,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B18" s="32">
         <v>48.6</v>
@@ -3282,13 +3294,18 @@
     </row>
     <row r="19" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B19" s="25">
         <v>27.9</v>
       </c>
       <c r="C19" s="26">
         <v>0.9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="47" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -3312,7 +3329,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -3342,43 +3359,43 @@
     </row>
     <row r="3" spans="1:12" ht="68.400000000000006" x14ac:dyDescent="0.3">
       <c r="A3" s="8"/>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="43" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="44" t="s">
+      <c r="H3" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="44" t="s">
+      <c r="I3" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="44" t="s">
+      <c r="J3" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="44" t="s">
+      <c r="K3" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="44" t="s">
+      <c r="L3" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="H3" s="44" t="s">
-        <v>50</v>
-      </c>
-      <c r="I3" s="44" t="s">
-        <v>51</v>
-      </c>
-      <c r="J3" s="44" t="s">
-        <v>52</v>
-      </c>
-      <c r="K3" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="L3" s="44" t="s">
-        <v>54</v>
-      </c>
     </row>
     <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="37" t="s">
-        <v>25</v>
+      <c r="A4" s="36" t="s">
+        <v>21</v>
       </c>
       <c r="B4" s="10">
         <v>8.6</v>
@@ -3432,7 +3449,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" s="8">
         <v>14.2</v>
@@ -3470,7 +3487,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" s="8">
         <v>9.9</v>
@@ -3774,7 +3791,7 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" s="8">
         <v>8.6999999999999993</v>
@@ -3812,7 +3829,7 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B16" s="8">
         <v>5</v>
@@ -3850,7 +3867,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B17" s="8">
         <v>5.0999999999999996</v>
@@ -3888,7 +3905,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" s="8">
         <v>4.2</v>
@@ -3926,7 +3943,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19" s="8">
         <v>5.5</v>
@@ -3964,7 +3981,7 @@
     </row>
     <row r="20" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20" s="10">
         <v>5.6</v>
@@ -4001,18 +4018,20 @@
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="35"/>
-      <c r="B21" s="36"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="36"/>
-      <c r="J21" s="36"/>
-      <c r="K21" s="36"/>
-      <c r="L21" s="36"/>
+      <c r="A21" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" s="35"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="35"/>
+      <c r="J21" s="35"/>
+      <c r="K21" s="35"/>
+      <c r="L21" s="35"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
